--- a/Gantt.xlsx
+++ b/Gantt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sujro\Documents\GitHub\Bachelor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA392357-F250-4DF9-8ABA-AF371A063CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B87150-9382-4C2C-A1FD-7F4A2D15BC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{C708630E-46F7-4A85-8DB4-933C05A31E60}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>January</t>
   </si>
@@ -132,6 +132,18 @@
   </si>
   <si>
     <t>Set up crane for cylinder force test</t>
+  </si>
+  <si>
+    <t>Mapping valve and cylinder characteristics</t>
+  </si>
+  <si>
+    <t>More advaced simscape model with data from mapping</t>
+  </si>
+  <si>
+    <t>Setup TwinCat for testing</t>
+  </si>
+  <si>
+    <t>Rapport writing</t>
   </si>
 </sst>
 </file>
@@ -183,7 +195,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,6 +238,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90CAF9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
     <border>
@@ -356,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -384,6 +402,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -420,11 +444,23 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,16 +470,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF80CBC4"/>
       <color rgb="FFA5D6A7"/>
       <color rgb="FFEF9A9A"/>
+      <color rgb="FFFFCC80"/>
+      <color rgb="FF90CAF9"/>
       <color rgb="FFCE93D8"/>
-      <color rgb="FF80CBC4"/>
-      <color rgb="FFFFCC80"/>
       <color rgb="FF009688"/>
       <color rgb="FF4CAF50"/>
       <color rgb="FFFF9800"/>
       <color rgb="FF9C27B0"/>
-      <color rgb="FFFFDB01"/>
     </mruColors>
   </colors>
   <extLst>
@@ -783,36 +819,36 @@
   <sheetData>
     <row r="3" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="4" spans="2:21" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="24" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="15" t="s">
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="24" t="s">
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="15" t="s">
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="17"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="19"/>
     </row>
     <row r="5" spans="2:21" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="1">
@@ -884,9 +920,11 @@
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="7"/>
+      <c r="G6" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="32"/>
+      <c r="I6" s="33"/>
       <c r="J6" s="8"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -902,18 +940,20 @@
     </row>
     <row r="7" spans="2:21" ht="15" x14ac:dyDescent="0.5">
       <c r="B7" s="8"/>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="21"/>
       <c r="F7" s="8"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="J7" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
       <c r="M7" s="7"/>
       <c r="N7" s="8"/>
       <c r="O7" s="6"/>
@@ -926,17 +966,19 @@
     </row>
     <row r="8" spans="2:21" ht="15" x14ac:dyDescent="0.5">
       <c r="B8" s="8"/>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="21"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="23"/>
       <c r="F8" s="8"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="6"/>
+      <c r="G8" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
       <c r="L8" s="6"/>
       <c r="M8" s="7"/>
       <c r="N8" s="8"/>
@@ -949,18 +991,20 @@
       <c r="U8" s="7"/>
     </row>
     <row r="9" spans="2:21" ht="15" x14ac:dyDescent="0.5">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="23"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="6"/>
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="6"/>
+      <c r="I9" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
       <c r="L9" s="6"/>
       <c r="M9" s="7"/>
       <c r="N9" s="8"/>
@@ -976,10 +1020,10 @@
       <c r="B10" s="8"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="15"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="7"/>
@@ -1000,10 +1044,10 @@
       <c r="B11" s="9"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="28"/>
+      <c r="F11" s="16"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="11"/>
@@ -1105,7 +1149,7 @@
       <c r="E21" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="R4:U4"/>
@@ -1116,6 +1160,10 @@
     <mergeCell ref="F4:I4"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="I9:K9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Gantt.xlsx
+++ b/Gantt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sujro\Documents\GitHub\Bachelor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimro\Documents\Bachelor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B87150-9382-4C2C-A1FD-7F4A2D15BC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36790378-07DD-4363-A284-97CDE765B38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{C708630E-46F7-4A85-8DB4-933C05A31E60}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C708630E-46F7-4A85-8DB4-933C05A31E60}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>January</t>
   </si>
@@ -125,32 +125,35 @@
     <t>Setup Github repo</t>
   </si>
   <si>
-    <t>Simple crane simscape modell</t>
-  </si>
-  <si>
     <t>Explore Simscape</t>
   </si>
   <si>
-    <t>Set up crane for cylinder force test</t>
-  </si>
-  <si>
-    <t>Mapping valve and cylinder characteristics</t>
-  </si>
-  <si>
     <t>More advaced simscape model with data from mapping</t>
   </si>
   <si>
-    <t>Setup TwinCat for testing</t>
-  </si>
-  <si>
-    <t>Rapport writing</t>
+    <t>Report writing</t>
+  </si>
+  <si>
+    <t>Simple crane simscape model</t>
+  </si>
+  <si>
+    <t>Twincat 3 development and testing</t>
+  </si>
+  <si>
+    <t>System characterisation</t>
+  </si>
+  <si>
+    <t>Identification of mechanical parameters</t>
+  </si>
+  <si>
+    <t>Modelling CBV and friction</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,7 +248,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -347,7 +350,69 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -359,7 +424,7 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -374,19 +439,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -402,64 +459,86 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -470,11 +549,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFEF9A9A"/>
+      <color rgb="FF90CAF9"/>
+      <color rgb="FFA5D6A7"/>
       <color rgb="FF80CBC4"/>
-      <color rgb="FFA5D6A7"/>
-      <color rgb="FFEF9A9A"/>
       <color rgb="FFFFCC80"/>
-      <color rgb="FF90CAF9"/>
       <color rgb="FFCE93D8"/>
       <color rgb="FF009688"/>
       <color rgb="FF4CAF50"/>
@@ -811,347 +890,355 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12C8378-5018-4125-A61A-6AFC813AA3BB}">
   <dimension ref="B3:U21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.86328125" customWidth="1"/>
-    <col min="2" max="21" width="17.59765625" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" customWidth="1"/>
+    <col min="2" max="21" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="4" spans="2:21" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="17" t="s">
+    <row r="3" spans="2:21" ht="15" thickBot="1"/>
+    <row r="4" spans="2:21" ht="15" thickBot="1">
+      <c r="B4" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="26" t="s">
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="17" t="s">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="26" t="s">
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="17" t="s">
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="19"/>
-    </row>
-    <row r="5" spans="2:21" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="1">
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="13"/>
+    </row>
+    <row r="5" spans="2:21" ht="15" thickBot="1">
+      <c r="B5" s="31">
         <v>2</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="32">
         <v>3</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="32">
         <v>4</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="34">
         <v>5</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="28">
         <v>6</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="35">
         <v>7</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="32">
         <v>8</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="34">
         <v>9</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="28">
         <v>10</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="35">
         <v>11</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="34">
         <v>12</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="1">
         <v>13</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="28">
         <v>14</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" s="35">
         <v>15</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="32">
         <v>16</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="34">
         <v>17</v>
       </c>
-      <c r="R5" s="1">
+      <c r="R5" s="28">
         <v>18</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="35">
         <v>19</v>
       </c>
-      <c r="T5" s="2">
+      <c r="T5" s="32">
         <v>20</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="33">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="15" x14ac:dyDescent="0.5">
-      <c r="B6" s="4" t="s">
+    <row r="6" spans="2:21">
+      <c r="B6" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="32" t="s">
+      <c r="C6" s="30"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="3"/>
+    </row>
+    <row r="7" spans="2:21">
+      <c r="B7" s="4"/>
+      <c r="C7" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="23"/>
+    </row>
+    <row r="8" spans="2:21">
+      <c r="B8" s="4"/>
+      <c r="C8" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="26"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="32"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="7"/>
-    </row>
-    <row r="7" spans="2:21" ht="15" x14ac:dyDescent="0.5">
-      <c r="B7" s="8"/>
-      <c r="C7" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="7"/>
-    </row>
-    <row r="8" spans="2:21" ht="15" x14ac:dyDescent="0.5">
-      <c r="B8" s="8"/>
-      <c r="C8" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="29" t="s">
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="2"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="3"/>
+    </row>
+    <row r="9" spans="2:21">
+      <c r="B9" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="23"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="3"/>
+    </row>
+    <row r="10" spans="2:21">
+      <c r="B10" s="4"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="7"/>
-    </row>
-    <row r="9" spans="2:21" ht="15" x14ac:dyDescent="0.5">
-      <c r="B9" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="34" t="s">
+      <c r="F10" s="21"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="3"/>
+    </row>
+    <row r="11" spans="2:21" ht="15" thickBot="1">
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="7"/>
-    </row>
-    <row r="10" spans="2:21" ht="15" x14ac:dyDescent="0.5">
-      <c r="B10" s="8"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="7"/>
-    </row>
-    <row r="11" spans="2:21" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="9"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="11"/>
-    </row>
-    <row r="15" spans="2:21" ht="15" x14ac:dyDescent="0.45">
-      <c r="B15" s="12" t="s">
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="7"/>
+    </row>
+    <row r="15" spans="2:21">
+      <c r="B15" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="12"/>
-    </row>
-    <row r="16" spans="2:21" ht="15" x14ac:dyDescent="0.45">
-      <c r="B16" s="13" t="s">
+      <c r="E15" s="8"/>
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" spans="2:21">
+      <c r="B16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="13"/>
-    </row>
-    <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.45">
-      <c r="B17" s="13" t="s">
+      <c r="E16" s="9"/>
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" spans="2:5" ht="28.8">
+      <c r="B17" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="13"/>
-    </row>
-    <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.45">
-      <c r="B18" s="13" t="s">
+      <c r="E17" s="9"/>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="13"/>
-    </row>
-    <row r="19" spans="2:5" ht="30" x14ac:dyDescent="0.45">
-      <c r="B19" s="13" t="s">
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" spans="2:5" ht="28.8">
+      <c r="B19" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="13"/>
-    </row>
-    <row r="20" spans="2:5" ht="30" x14ac:dyDescent="0.45">
-      <c r="B20" s="13" t="s">
+      <c r="E19" s="9"/>
+    </row>
+    <row r="20" spans="2:5" ht="28.8">
+      <c r="B20" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="13"/>
-    </row>
-    <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.45">
-      <c r="B21" s="13" t="s">
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21" spans="2:5" ht="28.8">
+      <c r="B21" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="13"/>
+      <c r="E21" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
+    <mergeCell ref="G6:O6"/>
+    <mergeCell ref="O7:U7"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="O9:Q9"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="R4:U4"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="C8:E8"/>
@@ -1162,7 +1249,6 @@
     <mergeCell ref="N4:Q4"/>
     <mergeCell ref="G8:K8"/>
     <mergeCell ref="J7:L7"/>
-    <mergeCell ref="G6:I6"/>
     <mergeCell ref="I9:K9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
